--- a/d2_urls.xlsx
+++ b/d2_urls.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="559">
   <si>
     <t>x</t>
   </si>
@@ -656,18 +656,216 @@
     <t>213</t>
   </si>
   <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>260</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/ee0af24d/Koln-Hamburger-SV-August-2-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b85153a5/Karlsruher-Nurnberg-August-3-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c1cd58b8/Hannover-96-Jahn-Regensburg-August-3-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6f5f7c69/Hertha-BSC-Paderborn-07-August-3-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b85153a5/Karlsruher-Nurnberg-August-3-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c1cd58b8/Hannover-96-Jahn-Regensburg-August-3-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c9c3d7eb/Magdeburg-Elversberg-August-3-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -677,27 +875,27 @@
     <t>https://fbref.com/en/matches/9f24ffef/Darmstadt-98-Dusseldorf-August-4-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/de3946b5/Greuther-Furth-Preussen-Munster-August-4-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/af4c88b7/Ulm-Kaiserslautern-August-4-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/de3946b5/Greuther-Furth-Preussen-Munster-August-4-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/96c41d6a/Jahn-Regensburg-Ulm-August-9-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/35824adb/Kaiserslautern-Greuther-Furth-August-9-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/96c41d6a/Jahn-Regensburg-Ulm-August-9-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/09d9ae86/Nurnberg-Schalke-04-August-10-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/55ab23e5/Elversberg-Koln-August-10-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/407f1ed1/Dusseldorf-Karlsruher-August-10-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/55ab23e5/Elversberg-Koln-August-10-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/cd504bf2/Hamburger-SV-Hertha-BSC-August-10-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -716,60 +914,60 @@
     <t>https://fbref.com/en/matches/e150fdc1/Hannover-96-Hamburger-SV-August-23-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9cc32a5f/Greuther-Furth-Paderborn-07-August-24-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6a7306c7/Preussen-Munster-Kaiserslautern-August-24-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/364c9353/Hertha-BSC-Jahn-Regensburg-August-24-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6a7306c7/Preussen-Munster-Kaiserslautern-August-24-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9cc32a5f/Greuther-Furth-Paderborn-07-August-24-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/211379ba/Koln-Eintracht-Braunschweig-August-24-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e159d11f/Ulm-Dusseldorf-August-25-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/34c2f883/Darmstadt-98-Nurnberg-August-25-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/e0a61214/Magdeburg-Schalke-04-August-25-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e159d11f/Ulm-Dusseldorf-August-25-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/02325837/Dusseldorf-Hannover-96-August-30-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/08f5ae1d/Jahn-Regensburg-Greuther-Furth-August-30-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/45368be3/Nurnberg-Magdeburg-August-31-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3e01d3a0/Elversberg-Darmstadt-98-August-31-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/45368be3/Nurnberg-Magdeburg-August-31-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/945579cf/Hamburger-SV-Preussen-Munster-August-31-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/71e1fcfb/Kaiserslautern-Hertha-BSC-August-31-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b1cd878f/Eintracht-Braunschweig-Karlsruher-September-1-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b2cc9318/Paderborn-07-Ulm-September-1-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3661b889/Schalke-04-Koln-September-1-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b1cd878f/Eintracht-Braunschweig-Karlsruher-September-1-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b2cc9318/Paderborn-07-Ulm-September-1-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/adae754a/Karlsruher-Schalke-04-September-13-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/2b1821d7/Preussen-Munster-Paderborn-07-September-13-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/adae754a/Karlsruher-Schalke-04-September-13-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/375b2727/Hannover-96-Kaiserslautern-September-14-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -782,12 +980,12 @@
     <t>https://fbref.com/en/matches/6f47c7c4/Koln-Magdeburg-September-14-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ab4a9b4f/Hertha-BSC-Dusseldorf-September-15-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1641fe3d/Greuther-Furth-Elversberg-September-15-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ab4a9b4f/Hertha-BSC-Dusseldorf-September-15-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d8bd433a/Hamburger-SV-Jahn-Regensburg-September-15-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -800,28 +998,31 @@
     <t>https://fbref.com/en/matches/5685e6d8/Dusseldorf-Koln-September-21-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e0717866/Eintracht-Braunschweig-Greuther-Furth-September-21-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5e86a5ce/Nurnberg-Hertha-BSC-September-21-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e0717866/Eintracht-Braunschweig-Greuther-Furth-September-21-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/50fb6408/Kaiserslautern-Hamburger-SV-September-21-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/51e5a246/Elversberg-Ulm-September-22-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/789689ab/Jahn-Regensburg-Preussen-Munster-September-22-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1812807a/Magdeburg-Karlsruher-September-22-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/51e5a246/Elversberg-Ulm-September-22-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/789689ab/Jahn-Regensburg-Preussen-Munster-September-22-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/c9aa1f29/Ulm-Eintracht-Braunschweig-September-27-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1a2ce577/Greuther-Furth-Dusseldorf-September-27-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c9aa1f29/Ulm-Eintracht-Braunschweig-September-27-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/b240225d/Darmstadt-98-Magdeburg-September-28-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/07fed62d/Hamburger-SV-Paderborn-07-September-28-2024-2-Bundesliga</t>
@@ -830,48 +1031,45 @@
     <t>https://fbref.com/en/matches/53ccd733/Jahn-Regensburg-Kaiserslautern-September-28-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b240225d/Darmstadt-98-Magdeburg-September-28-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/eccce024/Preussen-Munster-Schalke-04-September-28-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7806dbc9/Hannover-96-Nurnberg-September-29-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/423cd288/Hertha-BSC-Elversberg-September-29-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7806dbc9/Hannover-96-Nurnberg-September-29-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f3e71cb0/Koln-Karlsruher-September-29-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fa234ecd/Karlsruher-Darmstadt-98-October-4-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/e26d525b/Paderborn-07-Jahn-Regensburg-October-4-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fa234ecd/Karlsruher-Darmstadt-98-October-4-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/86d577fe/Koln-Ulm-October-5-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c21a122b/Nurnberg-Preussen-Munster-October-5-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/628732fa/Elversberg-Kaiserslautern-October-5-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/86d577fe/Koln-Ulm-October-5-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c21a122b/Nurnberg-Preussen-Munster-October-5-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f28f7197/Schalke-04-Hertha-BSC-October-5-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/6d8adfc1/Dusseldorf-Hamburger-SV-October-6-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6c03912d/Eintracht-Braunschweig-Hannover-96-October-6-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/14876931/Magdeburg-Greuther-Furth-October-6-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6c03912d/Eintracht-Braunschweig-Hannover-96-October-6-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/6d8adfc1/Dusseldorf-Hamburger-SV-October-6-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/84169840/Hertha-BSC-Eintracht-Braunschweig-October-18-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -905,15 +1103,15 @@
     <t>https://fbref.com/en/matches/bc5bf578/Koln-Paderborn-07-October-25-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fa08b089/Schalke-04-Greuther-Furth-October-26-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f1858d1c/Karlsruher-Hertha-BSC-October-26-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/f028f49c/Elversberg-Hamburger-SV-October-26-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f1858d1c/Karlsruher-Hertha-BSC-October-26-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fa08b089/Schalke-04-Greuther-Furth-October-26-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8b3f3eff/Dusseldorf-Kaiserslautern-October-26-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -944,39 +1142,39 @@
     <t>https://fbref.com/en/matches/b5875bb2/Hertha-BSC-Koln-November-2-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/45ee23a9/Paderborn-07-Eintracht-Braunschweig-November-3-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/30cb9be1/Kaiserslautern-Magdeburg-November-3-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/45ee23a9/Paderborn-07-Eintracht-Braunschweig-November-3-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/67ad107e/Hamburger-SV-Nurnberg-November-3-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/99c95367/Nurnberg-Kaiserslautern-November-8-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/850100a2/Eintracht-Braunschweig-Hamburger-SV-November-8-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/99c95367/Nurnberg-Kaiserslautern-November-8-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/f74703a9/Koln-Greuther-Furth-November-9-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c74caa02/Darmstadt-98-Hertha-BSC-November-9-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/c6f0f12b/Magdeburg-Ulm-November-9-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c74caa02/Darmstadt-98-Hertha-BSC-November-9-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f74703a9/Koln-Greuther-Furth-November-9-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e144fcaa/Dusseldorf-Paderborn-07-November-9-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/66553f06/Karlsruher-Preussen-Munster-November-10-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5b73e3bb/Elversberg-Hannover-96-November-10-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/66553f06/Karlsruher-Preussen-Munster-November-10-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8c2aa43e/Schalke-04-Jahn-Regensburg-November-10-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -986,60 +1184,60 @@
     <t>https://fbref.com/en/matches/be449b53/Preussen-Munster-Koln-November-22-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9c7cef3f/Dusseldorf-Elversberg-November-23-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9f18cc96/Hannover-96-Darmstadt-98-November-23-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/af9afab8/Hertha-BSC-Ulm-November-23-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3d6f6908/Greuther-Furth-Karlsruher-November-23-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9c7cef3f/Dusseldorf-Elversberg-November-23-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9f18cc96/Hannover-96-Darmstadt-98-November-23-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/af9afab8/Hertha-BSC-Ulm-November-23-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/51bef1bc/Hamburger-SV-Schalke-04-November-23-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7d985a73/Kaiserslautern-Eintracht-Braunschweig-November-24-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/33e26d8f/Jahn-Regensburg-Magdeburg-November-24-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7d985a73/Kaiserslautern-Eintracht-Braunschweig-November-24-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/71978cd9/Magdeburg-Hertha-BSC-November-29-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/40600890/Schalke-04-Kaiserslautern-November-29-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/71978cd9/Magdeburg-Hertha-BSC-November-29-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/4197f0d8/Koln-Hannover-96-November-30-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/3c1a7abd/Eintracht-Braunschweig-Jahn-Regensburg-November-30-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4197f0d8/Koln-Hannover-96-November-30-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/82b60a58/Elversberg-Paderborn-07-November-30-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/7d2e0153/Darmstadt-98-Preussen-Munster-November-30-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d7e0c72a/Karlsruher-Hamburger-SV-December-1-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/56903859/Ulm-Greuther-Furth-December-1-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/a4a5778d/Nurnberg-Dusseldorf-December-1-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d7e0c72a/Karlsruher-Hamburger-SV-December-1-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/f4204e2b/Elversberg-Nurnberg-December-6-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/d4c4d1ec/Paderborn-07-Schalke-04-December-6-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f4204e2b/Elversberg-Nurnberg-December-6-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4a05f145/Greuther-Furth-Hertha-BSC-December-7-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -1061,12 +1259,12 @@
     <t>https://fbref.com/en/matches/fe71798c/Hamburger-SV-Darmstadt-98-December-8-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7a8ec2d4/Hertha-BSC-Preussen-Munster-December-13-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/165cd623/Karlsruher-Jahn-Regensburg-December-13-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7a8ec2d4/Hertha-BSC-Preussen-Munster-December-13-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/69a37fe3/Schalke-04-Dusseldorf-December-14-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -1079,69 +1277,69 @@
     <t>https://fbref.com/en/matches/b25f4882/Darmstadt-98-Kaiserslautern-December-14-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fff95acf/Koln-Nurnberg-December-15-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d36afff1/Greuther-Furth-Hannover-96-December-15-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/593f5d49/Eintracht-Braunschweig-Elversberg-December-15-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d36afff1/Greuther-Furth-Hannover-96-December-15-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fff95acf/Koln-Nurnberg-December-15-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/f94607a0/Elversberg-Schalke-04-December-20-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/e2c61f93/Dusseldorf-Magdeburg-December-20-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f94607a0/Elversberg-Schalke-04-December-20-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/4e6fe54f/Paderborn-07-Karlsruher-December-21-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/53840007/Hamburger-SV-Greuther-Furth-December-21-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1cd7b86f/Preussen-Munster-Ulm-December-21-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4e6fe54f/Paderborn-07-Karlsruher-December-21-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/53840007/Hamburger-SV-Greuther-Furth-December-21-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/aa40c93b/Nurnberg-Eintracht-Braunschweig-December-21-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c82d2315/Kaiserslautern-Koln-December-22-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4faf0229/Hannover-96-Hertha-BSC-December-22-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0fe51571/Jahn-Regensburg-Darmstadt-98-December-22-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4faf0229/Hannover-96-Hertha-BSC-December-22-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c82d2315/Kaiserslautern-Koln-December-22-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/d96c4b24/Dusseldorf-Darmstadt-98-January-17-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/bfb9a612/Jahn-Regensburg-Hannover-96-January-17-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d96c4b24/Dusseldorf-Darmstadt-98-January-17-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/c3767fe4/Eintracht-Braunschweig-Schalke-04-January-18-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/030db051/Preussen-Munster-Greuther-Furth-January-18-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c3767fe4/Eintracht-Braunschweig-Schalke-04-January-18-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f06da604/Kaiserslautern-Ulm-January-18-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/fb85f8f0/Hamburger-SV-Koln-January-18-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3e372ba5/Elversberg-Magdeburg-January-19-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/aab3bcce/Nurnberg-Karlsruher-January-19-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1c546417/Paderborn-07-Hertha-BSC-January-19-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3e372ba5/Elversberg-Magdeburg-January-19-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/aab3bcce/Nurnberg-Karlsruher-January-19-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b6bec650/Greuther-Furth-Kaiserslautern-January-24-2025-2-Bundesliga</t>
   </si>
   <si>
@@ -1160,46 +1358,49 @@
     <t>https://fbref.com/en/matches/a629c8c1/Hertha-BSC-Hamburger-SV-January-25-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/cb5b26a4/Darmstadt-98-Paderborn-07-January-26-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6039d686/Ulm-Jahn-Regensburg-January-26-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/777b25c4/Hannover-96-Preussen-Munster-January-26-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/cb5b26a4/Darmstadt-98-Paderborn-07-January-26-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/b23641eb/Elversberg-Karlsruher-January-31-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/b0352c69/Nurnberg-Darmstadt-98-January-31-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b23641eb/Elversberg-Karlsruher-January-31-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/343e1bf9/Eintracht-Braunschweig-Koln-February-1-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c9d6312d/Dusseldorf-Ulm-February-1-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/0494cd25/Jahn-Regensburg-Hertha-BSC-February-1-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/343e1bf9/Eintracht-Braunschweig-Koln-February-1-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c9d6312d/Dusseldorf-Ulm-February-1-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4bd30b1a/Schalke-04-Magdeburg-February-1-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f13730c7/Kaiserslautern-Preussen-Munster-February-2-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/67e92610/Hamburger-SV-Hannover-96-February-2-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/c0d5015e/Paderborn-07-Greuther-Furth-February-2-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f13730c7/Kaiserslautern-Preussen-Munster-February-2-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/f92a545a/Preussen-Munster-Hamburger-SV-February-7-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/98b1a9e9/Greuther-Furth-Jahn-Regensburg-February-7-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f92a545a/Preussen-Munster-Hamburger-SV-February-7-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/fdaf5b2b/Magdeburg-Nurnberg-February-8-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/a7202223/Darmstadt-98-Elversberg-February-8-2025-2-Bundesliga</t>
@@ -1208,91 +1409,286 @@
     <t>https://fbref.com/en/matches/ec963bb2/Ulm-Paderborn-07-February-8-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fdaf5b2b/Magdeburg-Nurnberg-February-8-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3c43b1ed/Hertha-BSC-Kaiserslautern-February-8-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ce93e874/Koln-Schalke-04-February-9-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bc3cea21/Karlsruher-Eintracht-Braunschweig-February-9-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/64e2516d/Hannover-96-Dusseldorf-February-9-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bc3cea21/Karlsruher-Eintracht-Braunschweig-February-9-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ce93e874/Koln-Schalke-04-February-9-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/57717536/Paderborn-07-Preussen-Munster-February-14-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/c91ab13b/Magdeburg-Koln-February-14-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/aaf18b69/Eintracht-Braunschweig-Darmstadt-98-February-15-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/58f707ad/Kaiserslautern-Hannover-96-February-15-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/a514623a/Elversberg-Greuther-Furth-February-15-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/aaf18b69/Eintracht-Braunschweig-Darmstadt-98-February-15-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/923cbe35/Dusseldorf-Hertha-BSC-February-15-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f2edbe95/Schalke-04-Karlsruher-February-16-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/161cef36/Nurnberg-Ulm-February-16-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/2b8f17c1/Jahn-Regensburg-Hamburger-SV-February-16-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f2edbe95/Schalke-04-Karlsruher-February-16-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/1963f0d3/Hamburger-SV-Kaiserslautern-February-21-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/72f73361/Hertha-BSC-Nurnberg-February-21-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4067319a/Karlsruher-Magdeburg-February-22-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/09da0d27/Ulm-Elversberg-February-22-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4067319a/Karlsruher-Magdeburg-February-22-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/bf90c379/Preussen-Munster-Jahn-Regensburg-February-22-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/62e4f8d7/Hannover-96-Paderborn-07-February-22-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e46f44fc/Darmstadt-98-Schalke-04-February-23-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/30cb75d1/Greuther-Furth-Eintracht-Braunschweig-February-23-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/87fe0080/Koln-Dusseldorf-February-23-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e46f44fc/Darmstadt-98-Schalke-04-February-23-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/819d64f1/Schalke-04-Preussen-Munster-February-28-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/d4d7647f/Dusseldorf-Greuther-Furth-February-28-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/0c7f00e0/Eintracht-Braunschweig-Ulm-March-1-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/07774b89/Nurnberg-Hannover-96-March-1-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/04f201de/Kaiserslautern-Jahn-Regensburg-March-1-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/07774b89/Nurnberg-Hannover-96-March-1-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/0c7f00e0/Eintracht-Braunschweig-Ulm-March-1-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0a890979/Karlsruher-Koln-March-1-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5ee2b0e2/Magdeburg-Darmstadt-98-March-2-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d48aff6c/Paderborn-07-Hamburger-SV-March-2-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7a72c1ba/Elversberg-Hertha-BSC-March-2-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bc41571e/Darmstadt-98-Karlsruher-March-7-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c1880c18/Kaiserslautern-Elversberg-March-7-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3423d0c3/Greuther-Furth-Magdeburg-March-8-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3adab99a/Ulm-Koln-March-8-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8ba6d7be/Hertha-BSC-Schalke-04-March-8-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b669f5e2/Hamburger-SV-Dusseldorf-March-8-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6e140266/Preussen-Munster-Nurnberg-March-9-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9ac6df3b/Hannover-96-Eintracht-Braunschweig-March-9-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/61293c14/Jahn-Regensburg-Paderborn-07-March-9-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8e537c5d/Magdeburg-Hamburger-SV-March-14-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a1fbfd83/Schalke-04-Hannover-96-March-14-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/45751961/Elversberg-Preussen-Munster-March-15-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/145daec8/Dusseldorf-Jahn-Regensburg-March-15-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9fed77d4/Paderborn-07-Kaiserslautern-March-15-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b01b8cf6/Koln-Darmstadt-98-March-15-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2edacf1e/Nurnberg-Greuther-Furth-March-16-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3abfd0b1/Karlsruher-Ulm-March-16-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d6c8a30e/Eintracht-Braunschweig-Hertha-BSC-March-16-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/843f7627/Ulm-Darmstadt-98-March-28-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1df06926/Hamburger-SV-Elversberg-March-28-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/83f36dea/Hannover-96-Magdeburg-March-29-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e809149a/Hertha-BSC-Karlsruher-March-29-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/718eac70/Paderborn-07-Koln-March-29-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e17fb9f1/Kaiserslautern-Dusseldorf-March-29-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e04932b2/Jahn-Regensburg-Nurnberg-March-30-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b1505a7e/Preussen-Munster-Eintracht-Braunschweig-March-30-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9b9c0b53/Greuther-Furth-Schalke-04-March-30-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1dc7b91b/Karlsruher-Hannover-96-April-4-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2ac9ae98/Eintracht-Braunschweig-Paderborn-07-April-4-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/871dbf79/Nurnberg-Hamburger-SV-April-5-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dee4ef7f/Dusseldorf-Preussen-Munster-April-5-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/147aa0f5/Darmstadt-98-Greuther-Furth-April-5-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dd399f60/Koln-Hertha-BSC-April-5-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0f0df5d1/Magdeburg-Kaiserslautern-April-6-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2979e97a/Elversberg-Jahn-Regensburg-April-6-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2d334cfd/Schalke-04-Ulm-April-6-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/85494a71/Greuther-Furth-Koln-April-11-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2bf3003b/Hamburger-SV-Eintracht-Braunschweig-April-11-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b1b3e72e/Ulm-Magdeburg-April-12-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9466d0a8/Hertha-BSC-Darmstadt-98-April-12-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/93dbba6b/Hannover-96-Elversberg-April-12-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3f47e716/Kaiserslautern-Nurnberg-April-12-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4b1644a9/Paderborn-07-Dusseldorf-April-13-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7f403ef0/Preussen-Munster-Karlsruher-April-13-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e421a90d/Jahn-Regensburg-Schalke-04-April-13-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fa99f75a/Eintracht-Braunschweig-Kaiserslautern-April-19-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2bdb11d7/Elversberg-Dusseldorf-April-19-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0dfcbe53/Nurnberg-Paderborn-07-April-19-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5ee5ade4/Schalke-04-Hamburger-SV-April-19-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ea465160/Ulm-Hertha-BSC-April-20-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/da513244/Karlsruher-Greuther-Furth-April-20-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c7e5f277/Darmstadt-98-Hannover-96-April-20-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/34082514/Koln-Preussen-Munster-April-20-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9fbd4e95/Magdeburg-Jahn-Regensburg-April-20-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dbd08259/Hertha-BSC-Magdeburg-April-25-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/41f2cb37/Greuther-Furth-Ulm-April-25-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/df10e6a9/Preussen-Munster-Darmstadt-98-April-26-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d64b1296/Paderborn-07-Elversberg-April-26-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bdcde701/Jahn-Regensburg-Eintracht-Braunschweig-April-26-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0bd78d29/Dusseldorf-Nurnberg-April-26-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b3681e17/Hannover-96-Koln-April-27-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3d00c660/Hamburger-SV-Karlsruher-April-27-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/373ee0e9/Kaiserslautern-Schalke-04-April-27-2025-2-Bundesliga</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -1359,7 +1755,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>215</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4">
@@ -1367,7 +1763,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5">
@@ -1375,7 +1771,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>217</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6">
@@ -1383,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7">
@@ -1391,7 +1787,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8">
@@ -1399,7 +1795,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9">
@@ -1407,7 +1803,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -1415,7 +1811,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>222</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11">
@@ -1423,7 +1819,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>223</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12">
@@ -1431,7 +1827,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>224</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13">
@@ -1439,7 +1835,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>225</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14">
@@ -1447,7 +1843,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15">
@@ -1455,7 +1851,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>227</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -1463,7 +1859,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>228</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17">
@@ -1471,7 +1867,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>229</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18">
@@ -1479,7 +1875,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>230</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19">
@@ -1487,7 +1883,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>231</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20">
@@ -1495,7 +1891,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>232</v>
+        <v>298</v>
       </c>
     </row>
     <row r="21">
@@ -1503,7 +1899,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22">
@@ -1511,7 +1907,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>234</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23">
@@ -1519,7 +1915,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>235</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24">
@@ -1527,7 +1923,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>236</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25">
@@ -1535,7 +1931,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>237</v>
+        <v>303</v>
       </c>
     </row>
     <row r="26">
@@ -1543,7 +1939,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>238</v>
+        <v>304</v>
       </c>
     </row>
     <row r="27">
@@ -1551,7 +1947,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>239</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28">
@@ -1559,7 +1955,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>240</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29">
@@ -1567,7 +1963,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>241</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30">
@@ -1575,7 +1971,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>242</v>
+        <v>308</v>
       </c>
     </row>
     <row r="31">
@@ -1583,7 +1979,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>243</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32">
@@ -1591,7 +1987,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33">
@@ -1599,7 +1995,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>245</v>
+        <v>311</v>
       </c>
     </row>
     <row r="34">
@@ -1607,7 +2003,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>246</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35">
@@ -1615,7 +2011,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>247</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36">
@@ -1623,7 +2019,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>248</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37">
@@ -1631,7 +2027,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>249</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38">
@@ -1639,7 +2035,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>250</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39">
@@ -1647,7 +2043,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>251</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40">
@@ -1655,7 +2051,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41">
@@ -1663,7 +2059,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>253</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42">
@@ -1671,7 +2067,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>254</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43">
@@ -1679,7 +2075,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>255</v>
+        <v>321</v>
       </c>
     </row>
     <row r="44">
@@ -1687,7 +2083,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>256</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45">
@@ -1695,7 +2091,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>257</v>
+        <v>323</v>
       </c>
     </row>
     <row r="46">
@@ -1703,7 +2099,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>324</v>
       </c>
     </row>
     <row r="47">
@@ -1711,7 +2107,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>259</v>
+        <v>325</v>
       </c>
     </row>
     <row r="48">
@@ -1719,7 +2115,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>260</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49">
@@ -1727,7 +2123,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>261</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50">
@@ -1735,7 +2131,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>262</v>
+        <v>328</v>
       </c>
     </row>
     <row r="51">
@@ -1743,7 +2139,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>263</v>
+        <v>329</v>
       </c>
     </row>
     <row r="52">
@@ -1751,7 +2147,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>264</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53">
@@ -1759,7 +2155,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>265</v>
+        <v>331</v>
       </c>
     </row>
     <row r="54">
@@ -1767,7 +2163,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>266</v>
+        <v>332</v>
       </c>
     </row>
     <row r="55">
@@ -1775,7 +2171,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>267</v>
+        <v>333</v>
       </c>
     </row>
     <row r="56">
@@ -1783,7 +2179,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>268</v>
+        <v>334</v>
       </c>
     </row>
     <row r="57">
@@ -1791,7 +2187,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>269</v>
+        <v>335</v>
       </c>
     </row>
     <row r="58">
@@ -1799,7 +2195,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>270</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59">
@@ -1807,7 +2203,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>271</v>
+        <v>337</v>
       </c>
     </row>
     <row r="60">
@@ -1815,7 +2211,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>272</v>
+        <v>338</v>
       </c>
     </row>
     <row r="61">
@@ -1823,7 +2219,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>273</v>
+        <v>339</v>
       </c>
     </row>
     <row r="62">
@@ -1831,7 +2227,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>274</v>
+        <v>340</v>
       </c>
     </row>
     <row r="63">
@@ -1839,7 +2235,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
     </row>
     <row r="64">
@@ -1847,7 +2243,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>276</v>
+        <v>342</v>
       </c>
     </row>
     <row r="65">
@@ -1855,7 +2251,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>277</v>
+        <v>343</v>
       </c>
     </row>
     <row r="66">
@@ -1863,7 +2259,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>278</v>
+        <v>344</v>
       </c>
     </row>
     <row r="67">
@@ -1871,7 +2267,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>279</v>
+        <v>345</v>
       </c>
     </row>
     <row r="68">
@@ -1879,7 +2275,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
     </row>
     <row r="69">
@@ -1887,7 +2283,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>281</v>
+        <v>347</v>
       </c>
     </row>
     <row r="70">
@@ -1895,7 +2291,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>282</v>
+        <v>348</v>
       </c>
     </row>
     <row r="71">
@@ -1903,7 +2299,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
     </row>
     <row r="72">
@@ -1911,7 +2307,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
     </row>
     <row r="73">
@@ -1919,7 +2315,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>285</v>
+        <v>351</v>
       </c>
     </row>
     <row r="74">
@@ -1927,7 +2323,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>286</v>
+        <v>352</v>
       </c>
     </row>
     <row r="75">
@@ -1935,7 +2331,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>287</v>
+        <v>353</v>
       </c>
     </row>
     <row r="76">
@@ -1943,7 +2339,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>288</v>
+        <v>354</v>
       </c>
     </row>
     <row r="77">
@@ -1951,7 +2347,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>289</v>
+        <v>355</v>
       </c>
     </row>
     <row r="78">
@@ -1959,7 +2355,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>290</v>
+        <v>356</v>
       </c>
     </row>
     <row r="79">
@@ -1967,7 +2363,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>291</v>
+        <v>357</v>
       </c>
     </row>
     <row r="80">
@@ -1975,7 +2371,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>292</v>
+        <v>358</v>
       </c>
     </row>
     <row r="81">
@@ -1983,7 +2379,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>293</v>
+        <v>359</v>
       </c>
     </row>
     <row r="82">
@@ -1991,7 +2387,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>294</v>
+        <v>360</v>
       </c>
     </row>
     <row r="83">
@@ -1999,7 +2395,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>295</v>
+        <v>361</v>
       </c>
     </row>
     <row r="84">
@@ -2007,7 +2403,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>296</v>
+        <v>362</v>
       </c>
     </row>
     <row r="85">
@@ -2015,7 +2411,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>297</v>
+        <v>363</v>
       </c>
     </row>
     <row r="86">
@@ -2023,7 +2419,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>298</v>
+        <v>364</v>
       </c>
     </row>
     <row r="87">
@@ -2031,7 +2427,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>299</v>
+        <v>365</v>
       </c>
     </row>
     <row r="88">
@@ -2039,7 +2435,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>300</v>
+        <v>366</v>
       </c>
     </row>
     <row r="89">
@@ -2047,7 +2443,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>301</v>
+        <v>367</v>
       </c>
     </row>
     <row r="90">
@@ -2055,7 +2451,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>302</v>
+        <v>368</v>
       </c>
     </row>
     <row r="91">
@@ -2063,7 +2459,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>303</v>
+        <v>369</v>
       </c>
     </row>
     <row r="92">
@@ -2071,7 +2467,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>304</v>
+        <v>370</v>
       </c>
     </row>
     <row r="93">
@@ -2079,7 +2475,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>305</v>
+        <v>371</v>
       </c>
     </row>
     <row r="94">
@@ -2087,7 +2483,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>306</v>
+        <v>372</v>
       </c>
     </row>
     <row r="95">
@@ -2095,7 +2491,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>307</v>
+        <v>373</v>
       </c>
     </row>
     <row r="96">
@@ -2103,7 +2499,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>308</v>
+        <v>374</v>
       </c>
     </row>
     <row r="97">
@@ -2111,7 +2507,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>309</v>
+        <v>375</v>
       </c>
     </row>
     <row r="98">
@@ -2119,7 +2515,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>310</v>
+        <v>376</v>
       </c>
     </row>
     <row r="99">
@@ -2127,7 +2523,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>311</v>
+        <v>377</v>
       </c>
     </row>
     <row r="100">
@@ -2135,7 +2531,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>312</v>
+        <v>378</v>
       </c>
     </row>
     <row r="101">
@@ -2143,7 +2539,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>313</v>
+        <v>379</v>
       </c>
     </row>
     <row r="102">
@@ -2151,7 +2547,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>314</v>
+        <v>380</v>
       </c>
     </row>
     <row r="103">
@@ -2159,7 +2555,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>315</v>
+        <v>381</v>
       </c>
     </row>
     <row r="104">
@@ -2167,7 +2563,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>316</v>
+        <v>382</v>
       </c>
     </row>
     <row r="105">
@@ -2175,7 +2571,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>317</v>
+        <v>383</v>
       </c>
     </row>
     <row r="106">
@@ -2183,7 +2579,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>318</v>
+        <v>384</v>
       </c>
     </row>
     <row r="107">
@@ -2191,7 +2587,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>319</v>
+        <v>385</v>
       </c>
     </row>
     <row r="108">
@@ -2199,7 +2595,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>320</v>
+        <v>386</v>
       </c>
     </row>
     <row r="109">
@@ -2207,7 +2603,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>321</v>
+        <v>387</v>
       </c>
     </row>
     <row r="110">
@@ -2215,7 +2611,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>322</v>
+        <v>388</v>
       </c>
     </row>
     <row r="111">
@@ -2223,7 +2619,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>323</v>
+        <v>389</v>
       </c>
     </row>
     <row r="112">
@@ -2231,7 +2627,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
     </row>
     <row r="113">
@@ -2239,7 +2635,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
     </row>
     <row r="114">
@@ -2247,7 +2643,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
     </row>
     <row r="115">
@@ -2255,7 +2651,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
     </row>
     <row r="116">
@@ -2263,7 +2659,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="117">
@@ -2271,7 +2667,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
     </row>
     <row r="118">
@@ -2279,7 +2675,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
     </row>
     <row r="119">
@@ -2287,7 +2683,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="120">
@@ -2295,7 +2691,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>332</v>
+        <v>398</v>
       </c>
     </row>
     <row r="121">
@@ -2303,7 +2699,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>333</v>
+        <v>399</v>
       </c>
     </row>
     <row r="122">
@@ -2311,7 +2707,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="123">
@@ -2319,7 +2715,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>335</v>
+        <v>401</v>
       </c>
     </row>
     <row r="124">
@@ -2327,7 +2723,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>336</v>
+        <v>402</v>
       </c>
     </row>
     <row r="125">
@@ -2335,7 +2731,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>337</v>
+        <v>403</v>
       </c>
     </row>
     <row r="126">
@@ -2343,7 +2739,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>338</v>
+        <v>404</v>
       </c>
     </row>
     <row r="127">
@@ -2351,7 +2747,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>339</v>
+        <v>405</v>
       </c>
     </row>
     <row r="128">
@@ -2359,7 +2755,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>340</v>
+        <v>406</v>
       </c>
     </row>
     <row r="129">
@@ -2367,7 +2763,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>341</v>
+        <v>407</v>
       </c>
     </row>
     <row r="130">
@@ -2375,7 +2771,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>342</v>
+        <v>408</v>
       </c>
     </row>
     <row r="131">
@@ -2383,7 +2779,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>343</v>
+        <v>409</v>
       </c>
     </row>
     <row r="132">
@@ -2391,7 +2787,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>344</v>
+        <v>410</v>
       </c>
     </row>
     <row r="133">
@@ -2399,7 +2795,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>345</v>
+        <v>411</v>
       </c>
     </row>
     <row r="134">
@@ -2407,7 +2803,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>346</v>
+        <v>412</v>
       </c>
     </row>
     <row r="135">
@@ -2415,7 +2811,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>347</v>
+        <v>413</v>
       </c>
     </row>
     <row r="136">
@@ -2423,7 +2819,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>348</v>
+        <v>414</v>
       </c>
     </row>
     <row r="137">
@@ -2431,7 +2827,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>349</v>
+        <v>415</v>
       </c>
     </row>
     <row r="138">
@@ -2439,7 +2835,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>350</v>
+        <v>416</v>
       </c>
     </row>
     <row r="139">
@@ -2447,7 +2843,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>351</v>
+        <v>417</v>
       </c>
     </row>
     <row r="140">
@@ -2455,7 +2851,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>352</v>
+        <v>418</v>
       </c>
     </row>
     <row r="141">
@@ -2463,7 +2859,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>353</v>
+        <v>419</v>
       </c>
     </row>
     <row r="142">
@@ -2471,7 +2867,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>354</v>
+        <v>420</v>
       </c>
     </row>
     <row r="143">
@@ -2479,7 +2875,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>355</v>
+        <v>421</v>
       </c>
     </row>
     <row r="144">
@@ -2487,7 +2883,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>356</v>
+        <v>422</v>
       </c>
     </row>
     <row r="145">
@@ -2495,7 +2891,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>357</v>
+        <v>423</v>
       </c>
     </row>
     <row r="146">
@@ -2503,7 +2899,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>358</v>
+        <v>424</v>
       </c>
     </row>
     <row r="147">
@@ -2511,7 +2907,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>359</v>
+        <v>425</v>
       </c>
     </row>
     <row r="148">
@@ -2519,7 +2915,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>360</v>
+        <v>426</v>
       </c>
     </row>
     <row r="149">
@@ -2527,7 +2923,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>361</v>
+        <v>427</v>
       </c>
     </row>
     <row r="150">
@@ -2535,7 +2931,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>362</v>
+        <v>428</v>
       </c>
     </row>
     <row r="151">
@@ -2543,7 +2939,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>363</v>
+        <v>429</v>
       </c>
     </row>
     <row r="152">
@@ -2551,7 +2947,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>364</v>
+        <v>430</v>
       </c>
     </row>
     <row r="153">
@@ -2559,7 +2955,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>365</v>
+        <v>431</v>
       </c>
     </row>
     <row r="154">
@@ -2567,7 +2963,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>366</v>
+        <v>432</v>
       </c>
     </row>
     <row r="155">
@@ -2575,7 +2971,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>367</v>
+        <v>433</v>
       </c>
     </row>
     <row r="156">
@@ -2583,7 +2979,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>368</v>
+        <v>434</v>
       </c>
     </row>
     <row r="157">
@@ -2591,7 +2987,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>369</v>
+        <v>435</v>
       </c>
     </row>
     <row r="158">
@@ -2599,7 +2995,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>370</v>
+        <v>436</v>
       </c>
     </row>
     <row r="159">
@@ -2607,7 +3003,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>371</v>
+        <v>437</v>
       </c>
     </row>
     <row r="160">
@@ -2615,7 +3011,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
     </row>
     <row r="161">
@@ -2623,7 +3019,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>373</v>
+        <v>439</v>
       </c>
     </row>
     <row r="162">
@@ -2631,7 +3027,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>374</v>
+        <v>440</v>
       </c>
     </row>
     <row r="163">
@@ -2639,7 +3035,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>375</v>
+        <v>441</v>
       </c>
     </row>
     <row r="164">
@@ -2647,7 +3043,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>376</v>
+        <v>442</v>
       </c>
     </row>
     <row r="165">
@@ -2655,7 +3051,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>377</v>
+        <v>443</v>
       </c>
     </row>
     <row r="166">
@@ -2663,7 +3059,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>378</v>
+        <v>444</v>
       </c>
     </row>
     <row r="167">
@@ -2671,7 +3067,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="168">
@@ -2679,7 +3075,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>380</v>
+        <v>446</v>
       </c>
     </row>
     <row r="169">
@@ -2687,7 +3083,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>381</v>
+        <v>447</v>
       </c>
     </row>
     <row r="170">
@@ -2695,7 +3091,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>382</v>
+        <v>448</v>
       </c>
     </row>
     <row r="171">
@@ -2703,7 +3099,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>383</v>
+        <v>449</v>
       </c>
     </row>
     <row r="172">
@@ -2711,7 +3107,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>384</v>
+        <v>450</v>
       </c>
     </row>
     <row r="173">
@@ -2719,7 +3115,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>385</v>
+        <v>451</v>
       </c>
     </row>
     <row r="174">
@@ -2727,7 +3123,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>386</v>
+        <v>452</v>
       </c>
     </row>
     <row r="175">
@@ -2735,7 +3131,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>387</v>
+        <v>453</v>
       </c>
     </row>
     <row r="176">
@@ -2743,7 +3139,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>388</v>
+        <v>454</v>
       </c>
     </row>
     <row r="177">
@@ -2751,7 +3147,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>389</v>
+        <v>455</v>
       </c>
     </row>
     <row r="178">
@@ -2759,7 +3155,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>390</v>
+        <v>456</v>
       </c>
     </row>
     <row r="179">
@@ -2767,7 +3163,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>391</v>
+        <v>457</v>
       </c>
     </row>
     <row r="180">
@@ -2775,7 +3171,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>392</v>
+        <v>458</v>
       </c>
     </row>
     <row r="181">
@@ -2783,7 +3179,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>393</v>
+        <v>459</v>
       </c>
     </row>
     <row r="182">
@@ -2791,7 +3187,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>394</v>
+        <v>460</v>
       </c>
     </row>
     <row r="183">
@@ -2799,7 +3195,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>395</v>
+        <v>461</v>
       </c>
     </row>
     <row r="184">
@@ -2807,7 +3203,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>396</v>
+        <v>462</v>
       </c>
     </row>
     <row r="185">
@@ -2815,7 +3211,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>397</v>
+        <v>463</v>
       </c>
     </row>
     <row r="186">
@@ -2823,7 +3219,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>398</v>
+        <v>464</v>
       </c>
     </row>
     <row r="187">
@@ -2831,7 +3227,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>399</v>
+        <v>465</v>
       </c>
     </row>
     <row r="188">
@@ -2839,7 +3235,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>400</v>
+        <v>466</v>
       </c>
     </row>
     <row r="189">
@@ -2847,7 +3243,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>401</v>
+        <v>467</v>
       </c>
     </row>
     <row r="190">
@@ -2855,7 +3251,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>402</v>
+        <v>468</v>
       </c>
     </row>
     <row r="191">
@@ -2863,7 +3259,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>403</v>
+        <v>469</v>
       </c>
     </row>
     <row r="192">
@@ -2871,7 +3267,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>404</v>
+        <v>470</v>
       </c>
     </row>
     <row r="193">
@@ -2879,7 +3275,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>405</v>
+        <v>471</v>
       </c>
     </row>
     <row r="194">
@@ -2887,7 +3283,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +3291,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>407</v>
+        <v>473</v>
       </c>
     </row>
     <row r="196">
@@ -2903,7 +3299,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>408</v>
+        <v>474</v>
       </c>
     </row>
     <row r="197">
@@ -2911,7 +3307,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>409</v>
+        <v>475</v>
       </c>
     </row>
     <row r="198">
@@ -2919,7 +3315,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>410</v>
+        <v>476</v>
       </c>
     </row>
     <row r="199">
@@ -2927,7 +3323,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="200">
@@ -2935,7 +3331,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>412</v>
+        <v>478</v>
       </c>
     </row>
     <row r="201">
@@ -2943,7 +3339,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>413</v>
+        <v>479</v>
       </c>
     </row>
     <row r="202">
@@ -2951,7 +3347,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>414</v>
+        <v>480</v>
       </c>
     </row>
     <row r="203">
@@ -2959,7 +3355,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>415</v>
+        <v>481</v>
       </c>
     </row>
     <row r="204">
@@ -2967,7 +3363,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>416</v>
+        <v>482</v>
       </c>
     </row>
     <row r="205">
@@ -2975,7 +3371,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>417</v>
+        <v>483</v>
       </c>
     </row>
     <row r="206">
@@ -2983,7 +3379,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>418</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207">
@@ -2991,7 +3387,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>419</v>
+        <v>485</v>
       </c>
     </row>
     <row r="208">
@@ -2999,7 +3395,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>420</v>
+        <v>486</v>
       </c>
     </row>
     <row r="209">
@@ -3007,7 +3403,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>421</v>
+        <v>487</v>
       </c>
     </row>
     <row r="210">
@@ -3015,7 +3411,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>422</v>
+        <v>488</v>
       </c>
     </row>
     <row r="211">
@@ -3023,7 +3419,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>423</v>
+        <v>489</v>
       </c>
     </row>
     <row r="212">
@@ -3031,7 +3427,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>424</v>
+        <v>490</v>
       </c>
     </row>
     <row r="213">
@@ -3039,7 +3435,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>425</v>
+        <v>491</v>
       </c>
     </row>
     <row r="214">
@@ -3047,7 +3443,535 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>426</v>
+        <v>492</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>262</v>
+      </c>
+      <c r="B263" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>263</v>
+      </c>
+      <c r="B264" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>264</v>
+      </c>
+      <c r="B265" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>265</v>
+      </c>
+      <c r="B266" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>266</v>
+      </c>
+      <c r="B267" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>267</v>
+      </c>
+      <c r="B268" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>268</v>
+      </c>
+      <c r="B269" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>269</v>
+      </c>
+      <c r="B270" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>270</v>
+      </c>
+      <c r="B271" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>271</v>
+      </c>
+      <c r="B272" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>272</v>
+      </c>
+      <c r="B273" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>273</v>
+      </c>
+      <c r="B274" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>274</v>
+      </c>
+      <c r="B275" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>275</v>
+      </c>
+      <c r="B276" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>276</v>
+      </c>
+      <c r="B277" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>277</v>
+      </c>
+      <c r="B278" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>278</v>
+      </c>
+      <c r="B279" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>279</v>
+      </c>
+      <c r="B280" t="s">
+        <v>558</v>
       </c>
     </row>
   </sheetData>

--- a/d2_urls.xlsx
+++ b/d2_urls.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="621">
   <si>
     <t>x</t>
   </si>
@@ -854,9 +854,105 @@
     <t>279</t>
   </si>
   <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>287</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>291</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/ee0af24d/Koln-Hamburger-SV-August-2-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c9c3d7eb/Magdeburg-Elversberg-August-3-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b85153a5/Karlsruher-Nurnberg-August-3-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -866,48 +962,45 @@
     <t>https://fbref.com/en/matches/6f5f7c69/Hertha-BSC-Paderborn-07-August-3-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c9c3d7eb/Magdeburg-Elversberg-August-3-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ed2cb6b7/Schalke-04-Eintracht-Braunschweig-August-3-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/af4c88b7/Ulm-Kaiserslautern-August-4-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/de3946b5/Greuther-Furth-Preussen-Munster-August-4-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/9f24ffef/Darmstadt-98-Dusseldorf-August-4-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/de3946b5/Greuther-Furth-Preussen-Munster-August-4-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/af4c88b7/Ulm-Kaiserslautern-August-4-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/96c41d6a/Jahn-Regensburg-Ulm-August-9-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/35824adb/Kaiserslautern-Greuther-Furth-August-9-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/407f1ed1/Dusseldorf-Karlsruher-August-10-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/09d9ae86/Nurnberg-Schalke-04-August-10-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/55ab23e5/Elversberg-Koln-August-10-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/407f1ed1/Dusseldorf-Karlsruher-August-10-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/cd504bf2/Hamburger-SV-Hertha-BSC-August-10-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/64953f7c/Eintracht-Braunschweig-Magdeburg-August-11-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2761809f/Preussen-Munster-Hannover-96-August-11-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/3f33ad34/Paderborn-07-Darmstadt-98-August-11-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/64953f7c/Eintracht-Braunschweig-Magdeburg-August-11-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2e6bf2ff/Karlsruher-Elversberg-August-23-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -926,39 +1019,39 @@
     <t>https://fbref.com/en/matches/211379ba/Koln-Eintracht-Braunschweig-August-24-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e0a61214/Magdeburg-Schalke-04-August-25-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/e159d11f/Ulm-Dusseldorf-August-25-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/34c2f883/Darmstadt-98-Nurnberg-August-25-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e0a61214/Magdeburg-Schalke-04-August-25-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/08f5ae1d/Jahn-Regensburg-Greuther-Furth-August-30-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/02325837/Dusseldorf-Hannover-96-August-30-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/08f5ae1d/Jahn-Regensburg-Greuther-Furth-August-30-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/45368be3/Nurnberg-Magdeburg-August-31-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/945579cf/Hamburger-SV-Preussen-Munster-August-31-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3e01d3a0/Elversberg-Darmstadt-98-August-31-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/945579cf/Hamburger-SV-Preussen-Munster-August-31-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/71e1fcfb/Kaiserslautern-Hertha-BSC-August-31-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b2cc9318/Paderborn-07-Ulm-September-1-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b1cd878f/Eintracht-Braunschweig-Karlsruher-September-1-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b2cc9318/Paderborn-07-Ulm-September-1-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3661b889/Schalke-04-Koln-September-1-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -968,114 +1061,114 @@
     <t>https://fbref.com/en/matches/2b1821d7/Preussen-Munster-Paderborn-07-September-13-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ef5bc756/Ulm-Nurnberg-September-14-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/375b2727/Hannover-96-Kaiserslautern-September-14-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/6c3d4fbb/Darmstadt-98-Eintracht-Braunschweig-September-14-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ef5bc756/Ulm-Nurnberg-September-14-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6f47c7c4/Koln-Magdeburg-September-14-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d8bd433a/Hamburger-SV-Jahn-Regensburg-September-15-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1641fe3d/Greuther-Furth-Elversberg-September-15-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/ab4a9b4f/Hertha-BSC-Dusseldorf-September-15-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/1641fe3d/Greuther-Furth-Elversberg-September-15-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d8bd433a/Hamburger-SV-Jahn-Regensburg-September-15-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6f465e4c/Paderborn-07-Hannover-96-September-20-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/def69999/Schalke-04-Darmstadt-98-September-20-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/5e86a5ce/Nurnberg-Hertha-BSC-September-21-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e0717866/Eintracht-Braunschweig-Greuther-Furth-September-21-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5685e6d8/Dusseldorf-Koln-September-21-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e0717866/Eintracht-Braunschweig-Greuther-Furth-September-21-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/5e86a5ce/Nurnberg-Hertha-BSC-September-21-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/50fb6408/Kaiserslautern-Hamburger-SV-September-21-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/1812807a/Magdeburg-Karlsruher-September-22-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/789689ab/Jahn-Regensburg-Preussen-Munster-September-22-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/51e5a246/Elversberg-Ulm-September-22-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/789689ab/Jahn-Regensburg-Preussen-Munster-September-22-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/1812807a/Magdeburg-Karlsruher-September-22-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/1a2ce577/Greuther-Furth-Dusseldorf-September-27-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/c9aa1f29/Ulm-Eintracht-Braunschweig-September-27-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/1a2ce577/Greuther-Furth-Dusseldorf-September-27-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b240225d/Darmstadt-98-Magdeburg-September-28-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/53ccd733/Jahn-Regensburg-Kaiserslautern-September-28-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/07fed62d/Hamburger-SV-Paderborn-07-September-28-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/53ccd733/Jahn-Regensburg-Kaiserslautern-September-28-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/eccce024/Preussen-Munster-Schalke-04-September-28-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f3e71cb0/Koln-Karlsruher-September-29-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7806dbc9/Hannover-96-Nurnberg-September-29-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/423cd288/Hertha-BSC-Elversberg-September-29-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f3e71cb0/Koln-Karlsruher-September-29-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/e26d525b/Paderborn-07-Jahn-Regensburg-October-4-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/fa234ecd/Karlsruher-Darmstadt-98-October-4-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e26d525b/Paderborn-07-Jahn-Regensburg-October-4-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/c21a122b/Nurnberg-Preussen-Munster-October-5-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/628732fa/Elversberg-Kaiserslautern-October-5-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/86d577fe/Koln-Ulm-October-5-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c21a122b/Nurnberg-Preussen-Munster-October-5-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/628732fa/Elversberg-Kaiserslautern-October-5-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f28f7197/Schalke-04-Hertha-BSC-October-5-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/6c03912d/Eintracht-Braunschweig-Hannover-96-October-6-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6d8adfc1/Dusseldorf-Hamburger-SV-October-6-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6c03912d/Eintracht-Braunschweig-Hannover-96-October-6-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/14876931/Magdeburg-Greuther-Furth-October-6-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d46eedcd/Darmstadt-98-Koln-October-18-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/84169840/Hertha-BSC-Eintracht-Braunschweig-October-18-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d46eedcd/Darmstadt-98-Koln-October-18-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/03499101/Hannover-96-Schalke-04-October-19-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -1088,30 +1181,30 @@
     <t>https://fbref.com/en/matches/8d2d40c4/Kaiserslautern-Paderborn-07-October-19-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bdb9c218/Greuther-Furth-Nurnberg-October-20-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2a4d5aa3/Ulm-Karlsruher-October-20-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bdb9c218/Greuther-Furth-Nurnberg-October-20-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fa500c9e/Hamburger-SV-Magdeburg-October-20-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bc5bf578/Koln-Paderborn-07-October-25-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5c13efed/Nurnberg-Jahn-Regensburg-October-25-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bc5bf578/Koln-Paderborn-07-October-25-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/f028f49c/Elversberg-Hamburger-SV-October-26-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f1858d1c/Karlsruher-Hertha-BSC-October-26-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/fa08b089/Schalke-04-Greuther-Furth-October-26-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f1858d1c/Karlsruher-Hertha-BSC-October-26-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f028f49c/Elversberg-Hamburger-SV-October-26-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8b3f3eff/Dusseldorf-Kaiserslautern-October-26-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -1124,10 +1217,13 @@
     <t>https://fbref.com/en/matches/b089482e/Magdeburg-Hannover-96-October-27-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d597d3f1/Ulm-Schalke-04-November-1-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2014bb97/Preussen-Munster-Dusseldorf-November-1-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d597d3f1/Ulm-Schalke-04-November-1-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/e973f17f/Hannover-96-Karlsruher-November-2-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/6f50055e/Greuther-Furth-Darmstadt-98-November-2-2024-2-Bundesliga</t>
@@ -1136,33 +1232,30 @@
     <t>https://fbref.com/en/matches/b0ef73a4/Jahn-Regensburg-Elversberg-November-2-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e973f17f/Hannover-96-Karlsruher-November-2-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b5875bb2/Hertha-BSC-Koln-November-2-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/30cb9be1/Kaiserslautern-Magdeburg-November-3-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/45ee23a9/Paderborn-07-Eintracht-Braunschweig-November-3-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/30cb9be1/Kaiserslautern-Magdeburg-November-3-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/67ad107e/Hamburger-SV-Nurnberg-November-3-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/850100a2/Eintracht-Braunschweig-Hamburger-SV-November-8-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/99c95367/Nurnberg-Kaiserslautern-November-8-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/850100a2/Eintracht-Braunschweig-Hamburger-SV-November-8-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/c74caa02/Darmstadt-98-Hertha-BSC-November-9-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/f74703a9/Koln-Greuther-Furth-November-9-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c74caa02/Darmstadt-98-Hertha-BSC-November-9-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c6f0f12b/Magdeburg-Ulm-November-9-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -1172,30 +1265,30 @@
     <t>https://fbref.com/en/matches/66553f06/Karlsruher-Preussen-Munster-November-10-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8c2aa43e/Schalke-04-Jahn-Regensburg-November-10-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5b73e3bb/Elversberg-Hannover-96-November-10-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8c2aa43e/Schalke-04-Jahn-Regensburg-November-10-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/881964c8/Paderborn-07-Nurnberg-November-22-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/be449b53/Preussen-Munster-Koln-November-22-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3d6f6908/Greuther-Furth-Karlsruher-November-23-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/af9afab8/Hertha-BSC-Ulm-November-23-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9f18cc96/Hannover-96-Darmstadt-98-November-23-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/9c7cef3f/Dusseldorf-Elversberg-November-23-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9f18cc96/Hannover-96-Darmstadt-98-November-23-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/af9afab8/Hertha-BSC-Ulm-November-23-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/3d6f6908/Greuther-Furth-Karlsruher-November-23-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/51bef1bc/Hamburger-SV-Schalke-04-November-23-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -1211,33 +1304,33 @@
     <t>https://fbref.com/en/matches/40600890/Schalke-04-Kaiserslautern-November-29-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/82b60a58/Elversberg-Paderborn-07-November-30-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4197f0d8/Koln-Hannover-96-November-30-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/3c1a7abd/Eintracht-Braunschweig-Jahn-Regensburg-November-30-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/82b60a58/Elversberg-Paderborn-07-November-30-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/7d2e0153/Darmstadt-98-Preussen-Munster-November-30-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/56903859/Ulm-Greuther-Furth-December-1-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a4a5778d/Nurnberg-Dusseldorf-December-1-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/d7e0c72a/Karlsruher-Hamburger-SV-December-1-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/56903859/Ulm-Greuther-Furth-December-1-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/a4a5778d/Nurnberg-Dusseldorf-December-1-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/d4c4d1ec/Paderborn-07-Schalke-04-December-6-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/f4204e2b/Elversberg-Nurnberg-December-6-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d4c4d1ec/Paderborn-07-Schalke-04-December-6-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4a05f145/Greuther-Furth-Hertha-BSC-December-7-2024-2-Bundesliga</t>
   </si>
   <si>
@@ -1250,96 +1343,96 @@
     <t>https://fbref.com/en/matches/e9d30b14/Preussen-Munster-Magdeburg-December-7-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9eeb3a79/Jahn-Regensburg-Koln-December-8-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4c88f2d2/Dusseldorf-Eintracht-Braunschweig-December-8-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9eeb3a79/Jahn-Regensburg-Koln-December-8-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fe71798c/Hamburger-SV-Darmstadt-98-December-8-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/165cd623/Karlsruher-Jahn-Regensburg-December-13-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7a8ec2d4/Hertha-BSC-Preussen-Munster-December-13-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/165cd623/Karlsruher-Jahn-Regensburg-December-13-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/69a37fe3/Schalke-04-Dusseldorf-December-14-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/89cbe9f7/Magdeburg-Paderborn-07-December-14-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/75ec7446/Ulm-Hamburger-SV-December-14-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/89cbe9f7/Magdeburg-Paderborn-07-December-14-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b25f4882/Darmstadt-98-Kaiserslautern-December-14-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d36afff1/Greuther-Furth-Hannover-96-December-15-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/593f5d49/Eintracht-Braunschweig-Elversberg-December-15-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/fff95acf/Koln-Nurnberg-December-15-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d36afff1/Greuther-Furth-Hannover-96-December-15-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/593f5d49/Eintracht-Braunschweig-Elversberg-December-15-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f94607a0/Elversberg-Schalke-04-December-20-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/e2c61f93/Dusseldorf-Magdeburg-December-20-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/1cd7b86f/Preussen-Munster-Ulm-December-21-2024-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/53840007/Hamburger-SV-Greuther-Furth-December-21-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4e6fe54f/Paderborn-07-Karlsruher-December-21-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/53840007/Hamburger-SV-Greuther-Furth-December-21-2024-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/1cd7b86f/Preussen-Munster-Ulm-December-21-2024-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/aa40c93b/Nurnberg-Eintracht-Braunschweig-December-21-2024-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/c82d2315/Kaiserslautern-Koln-December-22-2024-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/0fe51571/Jahn-Regensburg-Darmstadt-98-December-22-2024-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4faf0229/Hannover-96-Hertha-BSC-December-22-2024-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/0fe51571/Jahn-Regensburg-Darmstadt-98-December-22-2024-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/bfb9a612/Jahn-Regensburg-Hannover-96-January-17-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/d96c4b24/Dusseldorf-Darmstadt-98-January-17-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bfb9a612/Jahn-Regensburg-Hannover-96-January-17-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/f06da604/Kaiserslautern-Ulm-January-18-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/030db051/Preussen-Munster-Greuther-Furth-January-18-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/c3767fe4/Eintracht-Braunschweig-Schalke-04-January-18-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/030db051/Preussen-Munster-Greuther-Furth-January-18-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f06da604/Kaiserslautern-Ulm-January-18-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fb85f8f0/Hamburger-SV-Koln-January-18-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/1c546417/Paderborn-07-Hertha-BSC-January-19-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3e372ba5/Elversberg-Magdeburg-January-19-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/aab3bcce/Nurnberg-Karlsruher-January-19-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/1c546417/Paderborn-07-Hertha-BSC-January-19-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b6bec650/Greuther-Furth-Kaiserslautern-January-24-2025-2-Bundesliga</t>
   </si>
   <si>
@@ -1358,48 +1451,48 @@
     <t>https://fbref.com/en/matches/a629c8c1/Hertha-BSC-Hamburger-SV-January-25-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/6039d686/Ulm-Jahn-Regensburg-January-26-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/cb5b26a4/Darmstadt-98-Paderborn-07-January-26-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6039d686/Ulm-Jahn-Regensburg-January-26-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/777b25c4/Hannover-96-Preussen-Munster-January-26-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b0352c69/Nurnberg-Darmstadt-98-January-31-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b23641eb/Elversberg-Karlsruher-January-31-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b0352c69/Nurnberg-Darmstadt-98-January-31-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/343e1bf9/Eintracht-Braunschweig-Koln-February-1-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/0494cd25/Jahn-Regensburg-Hertha-BSC-February-1-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/c9d6312d/Dusseldorf-Ulm-February-1-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/0494cd25/Jahn-Regensburg-Hertha-BSC-February-1-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4bd30b1a/Schalke-04-Magdeburg-February-1-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/67e92610/Hamburger-SV-Hannover-96-February-2-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/f13730c7/Kaiserslautern-Preussen-Munster-February-2-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/67e92610/Hamburger-SV-Hannover-96-February-2-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c0d5015e/Paderborn-07-Greuther-Furth-February-2-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/98b1a9e9/Greuther-Furth-Jahn-Regensburg-February-7-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/f92a545a/Preussen-Munster-Hamburger-SV-February-7-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/98b1a9e9/Greuther-Furth-Jahn-Regensburg-February-7-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fdaf5b2b/Magdeburg-Nurnberg-February-8-2025-2-Bundesliga</t>
   </si>
   <si>
@@ -1412,69 +1505,69 @@
     <t>https://fbref.com/en/matches/3c43b1ed/Hertha-BSC-Kaiserslautern-February-8-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/64e2516d/Hannover-96-Dusseldorf-February-9-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/ce93e874/Koln-Schalke-04-February-9-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/bc3cea21/Karlsruher-Eintracht-Braunschweig-February-9-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/64e2516d/Hannover-96-Dusseldorf-February-9-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/c91ab13b/Magdeburg-Koln-February-14-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/57717536/Paderborn-07-Preussen-Munster-February-14-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c91ab13b/Magdeburg-Koln-February-14-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/a514623a/Elversberg-Greuther-Furth-February-15-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/58f707ad/Kaiserslautern-Hannover-96-February-15-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/aaf18b69/Eintracht-Braunschweig-Darmstadt-98-February-15-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/58f707ad/Kaiserslautern-Hannover-96-February-15-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/a514623a/Elversberg-Greuther-Furth-February-15-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/923cbe35/Dusseldorf-Hertha-BSC-February-15-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/2b8f17c1/Jahn-Regensburg-Hamburger-SV-February-16-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/f2edbe95/Schalke-04-Karlsruher-February-16-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/161cef36/Nurnberg-Ulm-February-16-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/2b8f17c1/Jahn-Regensburg-Hamburger-SV-February-16-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/72f73361/Hertha-BSC-Nurnberg-February-21-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1963f0d3/Hamburger-SV-Kaiserslautern-February-21-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/72f73361/Hertha-BSC-Nurnberg-February-21-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4067319a/Karlsruher-Magdeburg-February-22-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bf90c379/Preussen-Munster-Jahn-Regensburg-February-22-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/09da0d27/Ulm-Elversberg-February-22-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bf90c379/Preussen-Munster-Jahn-Regensburg-February-22-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/62e4f8d7/Hannover-96-Paderborn-07-February-22-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/87fe0080/Koln-Dusseldorf-February-23-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/30cb75d1/Greuther-Furth-Eintracht-Braunschweig-February-23-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/e46f44fc/Darmstadt-98-Schalke-04-February-23-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/30cb75d1/Greuther-Furth-Eintracht-Braunschweig-February-23-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/87fe0080/Koln-Dusseldorf-February-23-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/819d64f1/Schalke-04-Preussen-Munster-February-28-2025-2-Bundesliga</t>
   </si>
   <si>
@@ -1493,66 +1586,66 @@
     <t>https://fbref.com/en/matches/0a890979/Karlsruher-Koln-March-1-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d48aff6c/Paderborn-07-Hamburger-SV-March-2-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7a72c1ba/Elversberg-Hertha-BSC-March-2-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5ee2b0e2/Magdeburg-Darmstadt-98-March-2-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d48aff6c/Paderborn-07-Hamburger-SV-March-2-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/7a72c1ba/Elversberg-Hertha-BSC-March-2-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/c1880c18/Kaiserslautern-Elversberg-March-7-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/bc41571e/Darmstadt-98-Karlsruher-March-7-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c1880c18/Kaiserslautern-Elversberg-March-7-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/3adab99a/Ulm-Koln-March-8-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/3423d0c3/Greuther-Furth-Magdeburg-March-8-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3adab99a/Ulm-Koln-March-8-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8ba6d7be/Hertha-BSC-Schalke-04-March-8-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/b669f5e2/Hamburger-SV-Dusseldorf-March-8-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9ac6df3b/Hannover-96-Eintracht-Braunschweig-March-9-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/61293c14/Jahn-Regensburg-Paderborn-07-March-9-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6e140266/Preussen-Munster-Nurnberg-March-9-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9ac6df3b/Hannover-96-Eintracht-Braunschweig-March-9-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/61293c14/Jahn-Regensburg-Paderborn-07-March-9-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8e537c5d/Magdeburg-Hamburger-SV-March-14-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/a1fbfd83/Schalke-04-Hannover-96-March-14-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/145daec8/Dusseldorf-Jahn-Regensburg-March-15-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/45751961/Elversberg-Preussen-Munster-March-15-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/145daec8/Dusseldorf-Jahn-Regensburg-March-15-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/9fed77d4/Paderborn-07-Kaiserslautern-March-15-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/b01b8cf6/Koln-Darmstadt-98-March-15-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3abfd0b1/Karlsruher-Ulm-March-16-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2edacf1e/Nurnberg-Greuther-Furth-March-16-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3abfd0b1/Karlsruher-Ulm-March-16-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d6c8a30e/Eintracht-Braunschweig-Hertha-BSC-March-16-2025-2-Bundesliga</t>
   </si>
   <si>
@@ -1562,51 +1655,51 @@
     <t>https://fbref.com/en/matches/1df06926/Hamburger-SV-Elversberg-March-28-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e809149a/Hertha-BSC-Karlsruher-March-29-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/718eac70/Paderborn-07-Koln-March-29-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/83f36dea/Hannover-96-Magdeburg-March-29-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e809149a/Hertha-BSC-Karlsruher-March-29-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/718eac70/Paderborn-07-Koln-March-29-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e17fb9f1/Kaiserslautern-Dusseldorf-March-29-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b1505a7e/Preussen-Munster-Eintracht-Braunschweig-March-30-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9b9c0b53/Greuther-Furth-Schalke-04-March-30-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/e04932b2/Jahn-Regensburg-Nurnberg-March-30-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b1505a7e/Preussen-Munster-Eintracht-Braunschweig-March-30-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9b9c0b53/Greuther-Furth-Schalke-04-March-30-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/2ac9ae98/Eintracht-Braunschweig-Paderborn-07-April-4-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1dc7b91b/Karlsruher-Hannover-96-April-4-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/2ac9ae98/Eintracht-Braunschweig-Paderborn-07-April-4-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/dee4ef7f/Dusseldorf-Preussen-Munster-April-5-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/871dbf79/Nurnberg-Hamburger-SV-April-5-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/dee4ef7f/Dusseldorf-Preussen-Munster-April-5-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/147aa0f5/Darmstadt-98-Greuther-Furth-April-5-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/dd399f60/Koln-Hertha-BSC-April-5-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/2979e97a/Elversberg-Jahn-Regensburg-April-6-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0f0df5d1/Magdeburg-Kaiserslautern-April-6-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/2979e97a/Elversberg-Jahn-Regensburg-April-6-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2d334cfd/Schalke-04-Ulm-April-6-2025-2-Bundesliga</t>
   </si>
   <si>
@@ -1616,15 +1709,15 @@
     <t>https://fbref.com/en/matches/2bf3003b/Hamburger-SV-Eintracht-Braunschweig-April-11-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/93dbba6b/Hannover-96-Elversberg-April-12-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9466d0a8/Hertha-BSC-Darmstadt-98-April-12-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b1b3e72e/Ulm-Magdeburg-April-12-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9466d0a8/Hertha-BSC-Darmstadt-98-April-12-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/93dbba6b/Hannover-96-Elversberg-April-12-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3f47e716/Kaiserslautern-Nurnberg-April-12-2025-2-Bundesliga</t>
   </si>
   <si>
@@ -1637,58 +1730,151 @@
     <t>https://fbref.com/en/matches/e421a90d/Jahn-Regensburg-Schalke-04-April-13-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/2bdb11d7/Elversberg-Dusseldorf-April-19-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0dfcbe53/Nurnberg-Paderborn-07-April-19-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/fa99f75a/Eintracht-Braunschweig-Kaiserslautern-April-19-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/2bdb11d7/Elversberg-Dusseldorf-April-19-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/0dfcbe53/Nurnberg-Paderborn-07-April-19-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/5ee5ade4/Schalke-04-Hamburger-SV-April-19-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/34082514/Koln-Preussen-Munster-April-20-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/ea465160/Ulm-Hertha-BSC-April-20-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9fbd4e95/Magdeburg-Jahn-Regensburg-April-20-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c7e5f277/Darmstadt-98-Hannover-96-April-20-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/da513244/Karlsruher-Greuther-Furth-April-20-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c7e5f277/Darmstadt-98-Hannover-96-April-20-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/34082514/Koln-Preussen-Munster-April-20-2025-2-Bundesliga</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9fbd4e95/Magdeburg-Jahn-Regensburg-April-20-2025-2-Bundesliga</t>
+    <t>https://fbref.com/en/matches/41f2cb37/Greuther-Furth-Ulm-April-25-2025-2-Bundesliga</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/dbd08259/Hertha-BSC-Magdeburg-April-25-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/41f2cb37/Greuther-Furth-Ulm-April-25-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/df10e6a9/Preussen-Munster-Darmstadt-98-April-26-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bdcde701/Jahn-Regensburg-Eintracht-Braunschweig-April-26-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/d64b1296/Paderborn-07-Elversberg-April-26-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bdcde701/Jahn-Regensburg-Eintracht-Braunschweig-April-26-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0bd78d29/Dusseldorf-Nurnberg-April-26-2025-2-Bundesliga</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3d00c660/Hamburger-SV-Karlsruher-April-27-2025-2-Bundesliga</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b3681e17/Hannover-96-Koln-April-27-2025-2-Bundesliga</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3d00c660/Hamburger-SV-Karlsruher-April-27-2025-2-Bundesliga</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/373ee0e9/Kaiserslautern-Schalke-04-April-27-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b9ff9627/Magdeburg-Preussen-Munster-May-2-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/752f3631/Schalke-04-Paderborn-07-May-2-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2226b7f5/Ulm-Hannover-96-May-3-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/52b36179/Darmstadt-98-Hamburger-SV-May-3-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/df2c5f65/Eintracht-Braunschweig-Dusseldorf-May-3-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8db7fc4e/Koln-Jahn-Regensburg-May-3-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4cb8ff6c/Nurnberg-Elversberg-May-4-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d3001924/Hertha-BSC-Greuther-Furth-May-4-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c8170b39/Karlsruher-Kaiserslautern-May-4-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f1160357/Nurnberg-Koln-May-9-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/abcf3225/Preussen-Munster-Hertha-BSC-May-9-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/28c22cda/Elversberg-Eintracht-Braunschweig-May-10-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/365f3050/Paderborn-07-Magdeburg-May-10-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1683d5d0/Dusseldorf-Schalke-04-May-10-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4e6d4f32/Hamburger-SV-Ulm-May-10-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/afa60be7/Kaiserslautern-Darmstadt-98-May-11-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a3cde090/Jahn-Regensburg-Karlsruher-May-11-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/92f57f19/Hannover-96-Greuther-Furth-May-11-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fe875378/Magdeburg-Dusseldorf-May-18-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c8bf4df9/Ulm-Preussen-Munster-May-18-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/30dd7ba0/Karlsruher-Paderborn-07-May-18-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f21f988c/Greuther-Furth-Hamburger-SV-May-18-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/49e5adbb/Hertha-BSC-Hannover-96-May-18-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/58aec426/Darmstadt-98-Jahn-Regensburg-May-18-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6359a04a/Eintracht-Braunschweig-Nurnberg-May-18-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e2ec8028/Koln-Kaiserslautern-May-18-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b196578b/Schalke-04-Elversberg-May-18-2025-2-Bundesliga</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ea16299e/Heidenheim-Elversberg-May-22-2025-German-12-RelegationPromotion-play-offs</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b1415fea/Saarbrucken-Eintracht-Braunschweig-May-23-2025-German-23-RelegationPromotion-play-offs</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/933eae7f/Elversberg-Heidenheim-May-26-2025-German-12-RelegationPromotion-play-offs</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6e2ce1fd/Eintracht-Braunschweig-Saarbrucken-May-27-2025-German-23-RelegationPromotion-play-offs</t>
   </si>
 </sst>
 </file>
@@ -1747,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3">
@@ -1755,7 +1941,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4">
@@ -1763,7 +1949,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5">
@@ -1771,7 +1957,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6">
@@ -1779,7 +1965,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7">
@@ -1787,7 +1973,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8">
@@ -1795,7 +1981,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
@@ -1803,7 +1989,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1811,7 +1997,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11">
@@ -1819,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12">
@@ -1827,7 +2013,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -1835,7 +2021,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14">
@@ -1843,7 +2029,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15">
@@ -1851,7 +2037,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16">
@@ -1859,7 +2045,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17">
@@ -1867,7 +2053,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18">
@@ -1875,7 +2061,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19">
@@ -1883,7 +2069,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20">
@@ -1891,7 +2077,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
     </row>
     <row r="21">
@@ -1899,7 +2085,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22">
@@ -1907,7 +2093,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
     </row>
     <row r="23">
@@ -1915,7 +2101,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24">
@@ -1923,7 +2109,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
     </row>
     <row r="25">
@@ -1931,7 +2117,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26">
@@ -1939,7 +2125,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27">
@@ -1947,7 +2133,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28">
@@ -1955,7 +2141,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29">
@@ -1963,7 +2149,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
     </row>
     <row r="30">
@@ -1971,7 +2157,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31">
@@ -1979,7 +2165,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32">
@@ -1987,7 +2173,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
     </row>
     <row r="33">
@@ -1995,7 +2181,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
     </row>
     <row r="34">
@@ -2003,7 +2189,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
     </row>
     <row r="35">
@@ -2011,7 +2197,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36">
@@ -2019,7 +2205,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
     </row>
     <row r="37">
@@ -2027,7 +2213,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
     </row>
     <row r="38">
@@ -2035,7 +2221,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
     </row>
     <row r="39">
@@ -2043,7 +2229,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
     </row>
     <row r="40">
@@ -2051,7 +2237,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41">
@@ -2059,7 +2245,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42">
@@ -2067,7 +2253,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43">
@@ -2075,7 +2261,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44">
@@ -2083,7 +2269,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
     </row>
     <row r="45">
@@ -2091,7 +2277,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
     </row>
     <row r="46">
@@ -2099,7 +2285,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
     </row>
     <row r="47">
@@ -2107,7 +2293,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
     </row>
     <row r="48">
@@ -2115,7 +2301,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
     </row>
     <row r="49">
@@ -2123,7 +2309,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
     </row>
     <row r="50">
@@ -2131,7 +2317,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
     </row>
     <row r="51">
@@ -2139,7 +2325,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
     </row>
     <row r="52">
@@ -2147,7 +2333,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
     </row>
     <row r="53">
@@ -2155,7 +2341,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
     </row>
     <row r="54">
@@ -2163,7 +2349,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55">
@@ -2171,7 +2357,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
     </row>
     <row r="56">
@@ -2179,7 +2365,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
     </row>
     <row r="57">
@@ -2187,7 +2373,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
     </row>
     <row r="58">
@@ -2195,7 +2381,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
     </row>
     <row r="59">
@@ -2203,7 +2389,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
     </row>
     <row r="60">
@@ -2211,7 +2397,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
     </row>
     <row r="61">
@@ -2219,7 +2405,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
     </row>
     <row r="62">
@@ -2227,7 +2413,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>340</v>
+        <v>371</v>
       </c>
     </row>
     <row r="63">
@@ -2235,7 +2421,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>341</v>
+        <v>372</v>
       </c>
     </row>
     <row r="64">
@@ -2243,7 +2429,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>342</v>
+        <v>373</v>
       </c>
     </row>
     <row r="65">
@@ -2251,7 +2437,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
     </row>
     <row r="66">
@@ -2259,7 +2445,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>344</v>
+        <v>375</v>
       </c>
     </row>
     <row r="67">
@@ -2267,7 +2453,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
     </row>
     <row r="68">
@@ -2275,7 +2461,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
     </row>
     <row r="69">
@@ -2283,7 +2469,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
     </row>
     <row r="70">
@@ -2291,7 +2477,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>348</v>
+        <v>379</v>
       </c>
     </row>
     <row r="71">
@@ -2299,7 +2485,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
     </row>
     <row r="72">
@@ -2307,7 +2493,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
     </row>
     <row r="73">
@@ -2315,7 +2501,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
     </row>
     <row r="74">
@@ -2323,7 +2509,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
     </row>
     <row r="75">
@@ -2331,7 +2517,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
     </row>
     <row r="76">
@@ -2339,7 +2525,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
     </row>
     <row r="77">
@@ -2347,7 +2533,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
     </row>
     <row r="78">
@@ -2355,7 +2541,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
     </row>
     <row r="79">
@@ -2363,7 +2549,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>357</v>
+        <v>388</v>
       </c>
     </row>
     <row r="80">
@@ -2371,7 +2557,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>358</v>
+        <v>389</v>
       </c>
     </row>
     <row r="81">
@@ -2379,7 +2565,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
     </row>
     <row r="82">
@@ -2387,7 +2573,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>360</v>
+        <v>391</v>
       </c>
     </row>
     <row r="83">
@@ -2395,7 +2581,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>361</v>
+        <v>392</v>
       </c>
     </row>
     <row r="84">
@@ -2403,7 +2589,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>362</v>
+        <v>393</v>
       </c>
     </row>
     <row r="85">
@@ -2411,7 +2597,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>363</v>
+        <v>394</v>
       </c>
     </row>
     <row r="86">
@@ -2419,7 +2605,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
     </row>
     <row r="87">
@@ -2427,7 +2613,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>365</v>
+        <v>396</v>
       </c>
     </row>
     <row r="88">
@@ -2435,7 +2621,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
     </row>
     <row r="89">
@@ -2443,7 +2629,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>367</v>
+        <v>398</v>
       </c>
     </row>
     <row r="90">
@@ -2451,7 +2637,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
     </row>
     <row r="91">
@@ -2459,7 +2645,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
     </row>
     <row r="92">
@@ -2467,7 +2653,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
     </row>
     <row r="93">
@@ -2475,7 +2661,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
     </row>
     <row r="94">
@@ -2483,7 +2669,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>372</v>
+        <v>403</v>
       </c>
     </row>
     <row r="95">
@@ -2491,7 +2677,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>373</v>
+        <v>404</v>
       </c>
     </row>
     <row r="96">
@@ -2499,7 +2685,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>374</v>
+        <v>405</v>
       </c>
     </row>
     <row r="97">
@@ -2507,7 +2693,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>375</v>
+        <v>406</v>
       </c>
     </row>
     <row r="98">
@@ -2515,7 +2701,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>376</v>
+        <v>407</v>
       </c>
     </row>
     <row r="99">
@@ -2523,7 +2709,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
     </row>
     <row r="100">
@@ -2531,7 +2717,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>378</v>
+        <v>409</v>
       </c>
     </row>
     <row r="101">
@@ -2539,7 +2725,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>379</v>
+        <v>410</v>
       </c>
     </row>
     <row r="102">
@@ -2547,7 +2733,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>380</v>
+        <v>411</v>
       </c>
     </row>
     <row r="103">
@@ -2555,7 +2741,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>381</v>
+        <v>412</v>
       </c>
     </row>
     <row r="104">
@@ -2563,7 +2749,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>382</v>
+        <v>413</v>
       </c>
     </row>
     <row r="105">
@@ -2571,7 +2757,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>383</v>
+        <v>414</v>
       </c>
     </row>
     <row r="106">
@@ -2579,7 +2765,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>384</v>
+        <v>415</v>
       </c>
     </row>
     <row r="107">
@@ -2587,7 +2773,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>385</v>
+        <v>416</v>
       </c>
     </row>
     <row r="108">
@@ -2595,7 +2781,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>386</v>
+        <v>417</v>
       </c>
     </row>
     <row r="109">
@@ -2603,7 +2789,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>387</v>
+        <v>418</v>
       </c>
     </row>
     <row r="110">
@@ -2611,7 +2797,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
     </row>
     <row r="111">
@@ -2619,7 +2805,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
     </row>
     <row r="112">
@@ -2627,7 +2813,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>390</v>
+        <v>421</v>
       </c>
     </row>
     <row r="113">
@@ -2635,7 +2821,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>391</v>
+        <v>422</v>
       </c>
     </row>
     <row r="114">
@@ -2643,7 +2829,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>392</v>
+        <v>423</v>
       </c>
     </row>
     <row r="115">
@@ -2651,7 +2837,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
     </row>
     <row r="116">
@@ -2659,7 +2845,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>394</v>
+        <v>425</v>
       </c>
     </row>
     <row r="117">
@@ -2667,7 +2853,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>395</v>
+        <v>426</v>
       </c>
     </row>
     <row r="118">
@@ -2675,7 +2861,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
     </row>
     <row r="119">
@@ -2683,7 +2869,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>397</v>
+        <v>428</v>
       </c>
     </row>
     <row r="120">
@@ -2691,7 +2877,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>398</v>
+        <v>429</v>
       </c>
     </row>
     <row r="121">
@@ -2699,7 +2885,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
     </row>
     <row r="122">
@@ -2707,7 +2893,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
     </row>
     <row r="123">
@@ -2715,7 +2901,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
     </row>
     <row r="124">
@@ -2723,7 +2909,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
     </row>
     <row r="125">
@@ -2731,7 +2917,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>403</v>
+        <v>434</v>
       </c>
     </row>
     <row r="126">
@@ -2739,7 +2925,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>404</v>
+        <v>435</v>
       </c>
     </row>
     <row r="127">
@@ -2747,7 +2933,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>405</v>
+        <v>436</v>
       </c>
     </row>
     <row r="128">
@@ -2755,7 +2941,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>406</v>
+        <v>437</v>
       </c>
     </row>
     <row r="129">
@@ -2763,7 +2949,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>407</v>
+        <v>438</v>
       </c>
     </row>
     <row r="130">
@@ -2771,7 +2957,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>408</v>
+        <v>439</v>
       </c>
     </row>
     <row r="131">
@@ -2779,7 +2965,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
     </row>
     <row r="132">
@@ -2787,7 +2973,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>410</v>
+        <v>441</v>
       </c>
     </row>
     <row r="133">
@@ -2795,7 +2981,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>411</v>
+        <v>442</v>
       </c>
     </row>
     <row r="134">
@@ -2803,7 +2989,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>412</v>
+        <v>443</v>
       </c>
     </row>
     <row r="135">
@@ -2811,7 +2997,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>413</v>
+        <v>444</v>
       </c>
     </row>
     <row r="136">
@@ -2819,7 +3005,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>414</v>
+        <v>445</v>
       </c>
     </row>
     <row r="137">
@@ -2827,7 +3013,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>415</v>
+        <v>446</v>
       </c>
     </row>
     <row r="138">
@@ -2835,7 +3021,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>416</v>
+        <v>447</v>
       </c>
     </row>
     <row r="139">
@@ -2843,7 +3029,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
     </row>
     <row r="140">
@@ -2851,7 +3037,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>418</v>
+        <v>449</v>
       </c>
     </row>
     <row r="141">
@@ -2859,7 +3045,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
     </row>
     <row r="142">
@@ -2867,7 +3053,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
     </row>
     <row r="143">
@@ -2875,7 +3061,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
     </row>
     <row r="144">
@@ -2883,7 +3069,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>422</v>
+        <v>453</v>
       </c>
     </row>
     <row r="145">
@@ -2891,7 +3077,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>423</v>
+        <v>454</v>
       </c>
     </row>
     <row r="146">
@@ -2899,7 +3085,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>424</v>
+        <v>455</v>
       </c>
     </row>
     <row r="147">
@@ -2907,7 +3093,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
     </row>
     <row r="148">
@@ -2915,7 +3101,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>426</v>
+        <v>457</v>
       </c>
     </row>
     <row r="149">
@@ -2923,7 +3109,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>427</v>
+        <v>458</v>
       </c>
     </row>
     <row r="150">
@@ -2931,7 +3117,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>428</v>
+        <v>459</v>
       </c>
     </row>
     <row r="151">
@@ -2939,7 +3125,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>429</v>
+        <v>460</v>
       </c>
     </row>
     <row r="152">
@@ -2947,7 +3133,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>430</v>
+        <v>461</v>
       </c>
     </row>
     <row r="153">
@@ -2955,7 +3141,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>431</v>
+        <v>462</v>
       </c>
     </row>
     <row r="154">
@@ -2963,7 +3149,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>432</v>
+        <v>463</v>
       </c>
     </row>
     <row r="155">
@@ -2971,7 +3157,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>433</v>
+        <v>464</v>
       </c>
     </row>
     <row r="156">
@@ -2979,7 +3165,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>434</v>
+        <v>465</v>
       </c>
     </row>
     <row r="157">
@@ -2987,7 +3173,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>435</v>
+        <v>466</v>
       </c>
     </row>
     <row r="158">
@@ -2995,7 +3181,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>436</v>
+        <v>467</v>
       </c>
     </row>
     <row r="159">
@@ -3003,7 +3189,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
     </row>
     <row r="160">
@@ -3011,7 +3197,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>438</v>
+        <v>469</v>
       </c>
     </row>
     <row r="161">
@@ -3019,7 +3205,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>439</v>
+        <v>470</v>
       </c>
     </row>
     <row r="162">
@@ -3027,7 +3213,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>440</v>
+        <v>471</v>
       </c>
     </row>
     <row r="163">
@@ -3035,7 +3221,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>441</v>
+        <v>472</v>
       </c>
     </row>
     <row r="164">
@@ -3043,7 +3229,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>442</v>
+        <v>473</v>
       </c>
     </row>
     <row r="165">
@@ -3051,7 +3237,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>443</v>
+        <v>474</v>
       </c>
     </row>
     <row r="166">
@@ -3059,7 +3245,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>444</v>
+        <v>475</v>
       </c>
     </row>
     <row r="167">
@@ -3067,7 +3253,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
     </row>
     <row r="168">
@@ -3075,7 +3261,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>446</v>
+        <v>477</v>
       </c>
     </row>
     <row r="169">
@@ -3083,7 +3269,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
     </row>
     <row r="170">
@@ -3091,7 +3277,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
     </row>
     <row r="171">
@@ -3099,7 +3285,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>449</v>
+        <v>480</v>
       </c>
     </row>
     <row r="172">
@@ -3107,7 +3293,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
     </row>
     <row r="173">
@@ -3115,7 +3301,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>451</v>
+        <v>482</v>
       </c>
     </row>
     <row r="174">
@@ -3123,7 +3309,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>452</v>
+        <v>483</v>
       </c>
     </row>
     <row r="175">
@@ -3131,7 +3317,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
     </row>
     <row r="176">
@@ -3139,7 +3325,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
     </row>
     <row r="177">
@@ -3147,7 +3333,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
     </row>
     <row r="178">
@@ -3155,7 +3341,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
     </row>
     <row r="179">
@@ -3163,7 +3349,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>457</v>
+        <v>488</v>
       </c>
     </row>
     <row r="180">
@@ -3171,7 +3357,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>458</v>
+        <v>489</v>
       </c>
     </row>
     <row r="181">
@@ -3179,7 +3365,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
     </row>
     <row r="182">
@@ -3187,7 +3373,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
     </row>
     <row r="183">
@@ -3195,7 +3381,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
     </row>
     <row r="184">
@@ -3203,7 +3389,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
     </row>
     <row r="185">
@@ -3211,7 +3397,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>463</v>
+        <v>494</v>
       </c>
     </row>
     <row r="186">
@@ -3219,7 +3405,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
     </row>
     <row r="187">
@@ -3227,7 +3413,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
     </row>
     <row r="188">
@@ -3235,7 +3421,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
     </row>
     <row r="189">
@@ -3243,7 +3429,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>467</v>
+        <v>498</v>
       </c>
     </row>
     <row r="190">
@@ -3251,7 +3437,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>468</v>
+        <v>499</v>
       </c>
     </row>
     <row r="191">
@@ -3259,7 +3445,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>469</v>
+        <v>500</v>
       </c>
     </row>
     <row r="192">
@@ -3267,7 +3453,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>470</v>
+        <v>501</v>
       </c>
     </row>
     <row r="193">
@@ -3275,7 +3461,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
     </row>
     <row r="194">
@@ -3283,7 +3469,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>472</v>
+        <v>503</v>
       </c>
     </row>
     <row r="195">
@@ -3291,7 +3477,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>473</v>
+        <v>504</v>
       </c>
     </row>
     <row r="196">
@@ -3299,7 +3485,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>474</v>
+        <v>505</v>
       </c>
     </row>
     <row r="197">
@@ -3307,7 +3493,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>475</v>
+        <v>506</v>
       </c>
     </row>
     <row r="198">
@@ -3315,7 +3501,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>476</v>
+        <v>507</v>
       </c>
     </row>
     <row r="199">
@@ -3323,7 +3509,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>477</v>
+        <v>508</v>
       </c>
     </row>
     <row r="200">
@@ -3331,7 +3517,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>478</v>
+        <v>509</v>
       </c>
     </row>
     <row r="201">
@@ -3339,7 +3525,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>479</v>
+        <v>510</v>
       </c>
     </row>
     <row r="202">
@@ -3347,7 +3533,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>480</v>
+        <v>511</v>
       </c>
     </row>
     <row r="203">
@@ -3355,7 +3541,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>481</v>
+        <v>512</v>
       </c>
     </row>
     <row r="204">
@@ -3363,7 +3549,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>482</v>
+        <v>513</v>
       </c>
     </row>
     <row r="205">
@@ -3371,7 +3557,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
     </row>
     <row r="206">
@@ -3379,7 +3565,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
     </row>
     <row r="207">
@@ -3387,7 +3573,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>485</v>
+        <v>516</v>
       </c>
     </row>
     <row r="208">
@@ -3395,7 +3581,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>486</v>
+        <v>517</v>
       </c>
     </row>
     <row r="209">
@@ -3403,7 +3589,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>487</v>
+        <v>518</v>
       </c>
     </row>
     <row r="210">
@@ -3411,7 +3597,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>488</v>
+        <v>519</v>
       </c>
     </row>
     <row r="211">
@@ -3419,7 +3605,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>489</v>
+        <v>520</v>
       </c>
     </row>
     <row r="212">
@@ -3427,7 +3613,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>490</v>
+        <v>521</v>
       </c>
     </row>
     <row r="213">
@@ -3435,7 +3621,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
     </row>
     <row r="214">
@@ -3443,7 +3629,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
     </row>
     <row r="215">
@@ -3451,7 +3637,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
     </row>
     <row r="216">
@@ -3459,7 +3645,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
     </row>
     <row r="217">
@@ -3467,7 +3653,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>495</v>
+        <v>526</v>
       </c>
     </row>
     <row r="218">
@@ -3475,7 +3661,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>496</v>
+        <v>527</v>
       </c>
     </row>
     <row r="219">
@@ -3483,7 +3669,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>497</v>
+        <v>528</v>
       </c>
     </row>
     <row r="220">
@@ -3491,7 +3677,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>498</v>
+        <v>529</v>
       </c>
     </row>
     <row r="221">
@@ -3499,7 +3685,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>499</v>
+        <v>530</v>
       </c>
     </row>
     <row r="222">
@@ -3507,7 +3693,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>500</v>
+        <v>531</v>
       </c>
     </row>
     <row r="223">
@@ -3515,7 +3701,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>501</v>
+        <v>532</v>
       </c>
     </row>
     <row r="224">
@@ -3523,7 +3709,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>502</v>
+        <v>533</v>
       </c>
     </row>
     <row r="225">
@@ -3531,7 +3717,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>503</v>
+        <v>534</v>
       </c>
     </row>
     <row r="226">
@@ -3539,7 +3725,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>504</v>
+        <v>535</v>
       </c>
     </row>
     <row r="227">
@@ -3547,7 +3733,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>505</v>
+        <v>536</v>
       </c>
     </row>
     <row r="228">
@@ -3555,7 +3741,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
     </row>
     <row r="229">
@@ -3563,7 +3749,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>507</v>
+        <v>538</v>
       </c>
     </row>
     <row r="230">
@@ -3571,7 +3757,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>508</v>
+        <v>539</v>
       </c>
     </row>
     <row r="231">
@@ -3579,7 +3765,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>509</v>
+        <v>540</v>
       </c>
     </row>
     <row r="232">
@@ -3587,7 +3773,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>510</v>
+        <v>541</v>
       </c>
     </row>
     <row r="233">
@@ -3595,7 +3781,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>511</v>
+        <v>542</v>
       </c>
     </row>
     <row r="234">
@@ -3603,7 +3789,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>512</v>
+        <v>543</v>
       </c>
     </row>
     <row r="235">
@@ -3611,7 +3797,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>513</v>
+        <v>544</v>
       </c>
     </row>
     <row r="236">
@@ -3619,7 +3805,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>514</v>
+        <v>545</v>
       </c>
     </row>
     <row r="237">
@@ -3627,7 +3813,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
     </row>
     <row r="238">
@@ -3635,7 +3821,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>516</v>
+        <v>547</v>
       </c>
     </row>
     <row r="239">
@@ -3643,7 +3829,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
     </row>
     <row r="240">
@@ -3651,7 +3837,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
     </row>
     <row r="241">
@@ -3659,7 +3845,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>519</v>
+        <v>550</v>
       </c>
     </row>
     <row r="242">
@@ -3667,7 +3853,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>520</v>
+        <v>551</v>
       </c>
     </row>
     <row r="243">
@@ -3675,7 +3861,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>521</v>
+        <v>552</v>
       </c>
     </row>
     <row r="244">
@@ -3683,7 +3869,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>522</v>
+        <v>553</v>
       </c>
     </row>
     <row r="245">
@@ -3691,7 +3877,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>523</v>
+        <v>554</v>
       </c>
     </row>
     <row r="246">
@@ -3699,7 +3885,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
     </row>
     <row r="247">
@@ -3707,7 +3893,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="248">
@@ -3715,7 +3901,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>526</v>
+        <v>557</v>
       </c>
     </row>
     <row r="249">
@@ -3723,7 +3909,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
     </row>
     <row r="250">
@@ -3731,7 +3917,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>528</v>
+        <v>559</v>
       </c>
     </row>
     <row r="251">
@@ -3739,7 +3925,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>529</v>
+        <v>560</v>
       </c>
     </row>
     <row r="252">
@@ -3747,7 +3933,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
     </row>
     <row r="253">
@@ -3755,7 +3941,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>531</v>
+        <v>562</v>
       </c>
     </row>
     <row r="254">
@@ -3763,7 +3949,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>532</v>
+        <v>563</v>
       </c>
     </row>
     <row r="255">
@@ -3771,7 +3957,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
     </row>
     <row r="256">
@@ -3779,7 +3965,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>534</v>
+        <v>565</v>
       </c>
     </row>
     <row r="257">
@@ -3787,7 +3973,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>535</v>
+        <v>566</v>
       </c>
     </row>
     <row r="258">
@@ -3795,7 +3981,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
     </row>
     <row r="259">
@@ -3803,7 +3989,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
     </row>
     <row r="260">
@@ -3811,7 +3997,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
     </row>
     <row r="261">
@@ -3819,7 +4005,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>539</v>
+        <v>570</v>
       </c>
     </row>
     <row r="262">
@@ -3827,7 +4013,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
     </row>
     <row r="263">
@@ -3835,7 +4021,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>541</v>
+        <v>572</v>
       </c>
     </row>
     <row r="264">
@@ -3843,7 +4029,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>542</v>
+        <v>573</v>
       </c>
     </row>
     <row r="265">
@@ -3851,7 +4037,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
     </row>
     <row r="266">
@@ -3859,7 +4045,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
     </row>
     <row r="267">
@@ -3867,7 +4053,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
     </row>
     <row r="268">
@@ -3875,7 +4061,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="269">
@@ -3883,7 +4069,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>547</v>
+        <v>578</v>
       </c>
     </row>
     <row r="270">
@@ -3891,7 +4077,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>548</v>
+        <v>579</v>
       </c>
     </row>
     <row r="271">
@@ -3899,7 +4085,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>549</v>
+        <v>580</v>
       </c>
     </row>
     <row r="272">
@@ -3907,7 +4093,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
     </row>
     <row r="273">
@@ -3915,7 +4101,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>551</v>
+        <v>582</v>
       </c>
     </row>
     <row r="274">
@@ -3923,7 +4109,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
     </row>
     <row r="275">
@@ -3931,7 +4117,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
     </row>
     <row r="276">
@@ -3939,7 +4125,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
     </row>
     <row r="277">
@@ -3947,7 +4133,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>555</v>
+        <v>586</v>
       </c>
     </row>
     <row r="278">
@@ -3955,7 +4141,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>556</v>
+        <v>587</v>
       </c>
     </row>
     <row r="279">
@@ -3963,7 +4149,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
     </row>
     <row r="280">
@@ -3971,7 +4157,255 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>558</v>
+        <v>589</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>280</v>
+      </c>
+      <c r="B281" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>281</v>
+      </c>
+      <c r="B282" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>282</v>
+      </c>
+      <c r="B283" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>283</v>
+      </c>
+      <c r="B284" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>284</v>
+      </c>
+      <c r="B285" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>285</v>
+      </c>
+      <c r="B286" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>286</v>
+      </c>
+      <c r="B287" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>287</v>
+      </c>
+      <c r="B288" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>288</v>
+      </c>
+      <c r="B289" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>289</v>
+      </c>
+      <c r="B290" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>290</v>
+      </c>
+      <c r="B291" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>291</v>
+      </c>
+      <c r="B292" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>292</v>
+      </c>
+      <c r="B293" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>293</v>
+      </c>
+      <c r="B294" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>294</v>
+      </c>
+      <c r="B295" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>295</v>
+      </c>
+      <c r="B296" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>296</v>
+      </c>
+      <c r="B297" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>297</v>
+      </c>
+      <c r="B298" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>298</v>
+      </c>
+      <c r="B299" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>299</v>
+      </c>
+      <c r="B300" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>300</v>
+      </c>
+      <c r="B301" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>301</v>
+      </c>
+      <c r="B302" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>302</v>
+      </c>
+      <c r="B303" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>303</v>
+      </c>
+      <c r="B304" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>304</v>
+      </c>
+      <c r="B305" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>305</v>
+      </c>
+      <c r="B306" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>306</v>
+      </c>
+      <c r="B307" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>307</v>
+      </c>
+      <c r="B308" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>308</v>
+      </c>
+      <c r="B309" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>309</v>
+      </c>
+      <c r="B310" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>310</v>
+      </c>
+      <c r="B311" t="s">
+        <v>620</v>
       </c>
     </row>
   </sheetData>
